--- a/HEDIS_POC_All_20_Members.xlsx
+++ b/HEDIS_POC_All_20_Members.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Kavya\Hedis-ai-ashi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CB66A3D1-199C-4C37-A29D-3F7987B14C61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B38DC56-64C5-42AF-AB43-4D4B44153A45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Member_Profile" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="609" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="694" uniqueCount="324">
   <si>
     <t>Member ID</t>
   </si>
@@ -882,13 +882,127 @@
   </si>
   <si>
     <t>viditrajput18@gmail.com</t>
+  </si>
+  <si>
+    <t>Nearest Hospital</t>
+  </si>
+  <si>
+    <t>Valley Health Medical Center</t>
+  </si>
+  <si>
+    <t>Northwell Medical Group</t>
+  </si>
+  <si>
+    <t>Sunrise Family Care Center</t>
+  </si>
+  <si>
+    <t>Riverside Community Hospital</t>
+  </si>
+  <si>
+    <t>St. Mary's Medical Center</t>
+  </si>
+  <si>
+    <t>Mercy General Hospital</t>
+  </si>
+  <si>
+    <t>Westbrook Healthcare Center</t>
+  </si>
+  <si>
+    <t>Cedar Grove Family Clinic</t>
+  </si>
+  <si>
+    <t>Healthcare Address</t>
+  </si>
+  <si>
+    <t>770 Lakeside Drive, Orlando, FL</t>
+  </si>
+  <si>
+    <t>250 Evergreen Blvd, Seattle, WA</t>
+  </si>
+  <si>
+    <t>920 Sunrise Highway, Miami, FL</t>
+  </si>
+  <si>
+    <t>4445 Magnolia Ave, Riverside, CA</t>
+  </si>
+  <si>
+    <t>1200 Cedar Ave, Phoenix, AZ</t>
+  </si>
+  <si>
+    <t>4500 Oak Street, Los Angeles, CA</t>
+  </si>
+  <si>
+    <t>8900 Brookside Dr, Dallas, TX</t>
+  </si>
+  <si>
+    <t>1111 Hempstead Turnpike, New Hyde Park, NY</t>
+  </si>
+  <si>
+    <t>Provider Name</t>
+  </si>
+  <si>
+    <t>Dr. Sarah Thompson</t>
+  </si>
+  <si>
+    <t>Dr. Christopher Miller</t>
+  </si>
+  <si>
+    <t>Dr. Olivia Martinez</t>
+  </si>
+  <si>
+    <t>Dr. Jennifer Wilson</t>
+  </si>
+  <si>
+    <t>Dr. Robert Taylor</t>
+  </si>
+  <si>
+    <t>Dr. Emily Carter</t>
+  </si>
+  <si>
+    <t>Dr. Michael Johnson</t>
+  </si>
+  <si>
+    <t>Dr. Sophia White</t>
+  </si>
+  <si>
+    <t>Dr. David Anderson</t>
+  </si>
+  <si>
+    <t>Dr. James Walker</t>
+  </si>
+  <si>
+    <t>Provider Specialty</t>
+  </si>
+  <si>
+    <t>Family Medicine</t>
+  </si>
+  <si>
+    <t>Internal Medicine</t>
+  </si>
+  <si>
+    <t>Cardiology</t>
+  </si>
+  <si>
+    <t>Preventive Care</t>
+  </si>
+  <si>
+    <t>Women's Health</t>
+  </si>
+  <si>
+    <t>Primary Care</t>
+  </si>
+  <si>
+    <t>Pediatrics</t>
+  </si>
+  <si>
+    <t>Distance To Provider (Miles)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -909,6 +1023,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -918,7 +1040,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -926,15 +1048,50 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1238,10 +1395,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F21"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:K21"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="6" max="6" width="33.140625" customWidth="1"/>
+    <col min="7" max="7" width="29.140625" customWidth="1"/>
+    <col min="8" max="8" width="43.28515625" customWidth="1"/>
+    <col min="9" max="9" width="39.42578125" customWidth="1"/>
+    <col min="10" max="10" width="19.140625" customWidth="1"/>
+    <col min="11" max="11" width="26.5703125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1260,8 +1425,23 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G1" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>295</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>304</v>
+      </c>
+      <c r="J1" s="10" t="s">
+        <v>315</v>
+      </c>
+      <c r="K1" s="12" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -1280,8 +1460,23 @@
       <c r="F2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G2" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>316</v>
+      </c>
+      <c r="K2" s="11">
+        <v>13.3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -1300,8 +1495,23 @@
       <c r="F3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G3" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>306</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>317</v>
+      </c>
+      <c r="K3" s="11">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -1320,8 +1530,23 @@
       <c r="F4" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G4" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>317</v>
+      </c>
+      <c r="K4" s="11">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -1340,8 +1565,23 @@
       <c r="F5" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G5" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>318</v>
+      </c>
+      <c r="K5" s="11">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>26</v>
       </c>
@@ -1360,8 +1600,23 @@
       <c r="F6" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G6" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="J6" s="9" t="s">
+        <v>319</v>
+      </c>
+      <c r="K6" s="11">
+        <v>16.7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -1380,8 +1635,23 @@
       <c r="F7" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G7" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>310</v>
+      </c>
+      <c r="J7" s="9" t="s">
+        <v>320</v>
+      </c>
+      <c r="K7" s="11">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>35</v>
       </c>
@@ -1400,8 +1670,23 @@
       <c r="F8" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G8" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="I8" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="J8" s="9" t="s">
+        <v>321</v>
+      </c>
+      <c r="K8" s="11">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>39</v>
       </c>
@@ -1420,8 +1705,23 @@
       <c r="F9" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G9" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="J9" s="9" t="s">
+        <v>321</v>
+      </c>
+      <c r="K9" s="11">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>44</v>
       </c>
@@ -1440,8 +1740,23 @@
       <c r="F10" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G10" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="I10" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="J10" s="9" t="s">
+        <v>320</v>
+      </c>
+      <c r="K10" s="11">
+        <v>16.100000000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>48</v>
       </c>
@@ -1460,8 +1775,23 @@
       <c r="F11" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G11" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="I11" s="7" t="s">
+        <v>312</v>
+      </c>
+      <c r="J11" s="9" t="s">
+        <v>321</v>
+      </c>
+      <c r="K11" s="11">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>53</v>
       </c>
@@ -1480,8 +1810,23 @@
       <c r="F12" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G12" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="I12" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="J12" s="9" t="s">
+        <v>320</v>
+      </c>
+      <c r="K12" s="11">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>57</v>
       </c>
@@ -1500,8 +1845,23 @@
       <c r="F13" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G13" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="I13" s="7" t="s">
+        <v>310</v>
+      </c>
+      <c r="J13" s="9" t="s">
+        <v>322</v>
+      </c>
+      <c r="K13" s="11">
+        <v>4.5999999999999996</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>62</v>
       </c>
@@ -1520,8 +1880,23 @@
       <c r="F14" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G14" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="I14" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="J14" s="9" t="s">
+        <v>319</v>
+      </c>
+      <c r="K14" s="11">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>66</v>
       </c>
@@ -1540,8 +1915,23 @@
       <c r="F15" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G15" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="I15" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="J15" s="9" t="s">
+        <v>316</v>
+      </c>
+      <c r="K15" s="11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>71</v>
       </c>
@@ -1560,8 +1950,23 @@
       <c r="F16" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G16" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="I16" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="J16" s="9" t="s">
+        <v>318</v>
+      </c>
+      <c r="K16" s="11">
+        <v>8.3000000000000007</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>75</v>
       </c>
@@ -1580,8 +1985,23 @@
       <c r="F17" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G17" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="I17" s="7" t="s">
+        <v>314</v>
+      </c>
+      <c r="J17" s="9" t="s">
+        <v>318</v>
+      </c>
+      <c r="K17" s="11">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>80</v>
       </c>
@@ -1600,8 +2020,23 @@
       <c r="F18" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G18" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="I18" s="7" t="s">
+        <v>314</v>
+      </c>
+      <c r="J18" s="9" t="s">
+        <v>322</v>
+      </c>
+      <c r="K18" s="11">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>84</v>
       </c>
@@ -1620,8 +2055,23 @@
       <c r="F19" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G19" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="I19" s="7" t="s">
+        <v>312</v>
+      </c>
+      <c r="J19" s="9" t="s">
+        <v>320</v>
+      </c>
+      <c r="K19" s="11">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>89</v>
       </c>
@@ -1640,8 +2090,23 @@
       <c r="F20" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G20" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="I20" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="J20" s="9" t="s">
+        <v>318</v>
+      </c>
+      <c r="K20" s="11">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>94</v>
       </c>
@@ -1659,6 +2124,21 @@
       </c>
       <c r="F21" t="s">
         <v>98</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="I21" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="J21" s="9" t="s">
+        <v>318</v>
+      </c>
+      <c r="K21" s="11">
+        <v>8.8000000000000007</v>
       </c>
     </row>
   </sheetData>
@@ -1680,9 +2160,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D21"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>99</v>
       </c>
@@ -1696,7 +2176,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>103</v>
       </c>
@@ -1710,7 +2190,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>107</v>
       </c>
@@ -1724,7 +2204,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>111</v>
       </c>
@@ -1738,7 +2218,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>103</v>
       </c>
@@ -1752,7 +2232,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>107</v>
       </c>
@@ -1766,7 +2246,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>111</v>
       </c>
@@ -1780,7 +2260,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>103</v>
       </c>
@@ -1794,7 +2274,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>107</v>
       </c>
@@ -1808,7 +2288,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>111</v>
       </c>
@@ -1822,7 +2302,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>103</v>
       </c>
@@ -1836,7 +2316,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>107</v>
       </c>
@@ -1850,7 +2330,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>111</v>
       </c>
@@ -1864,7 +2344,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>103</v>
       </c>
@@ -1878,7 +2358,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>107</v>
       </c>
@@ -1892,7 +2372,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>111</v>
       </c>
@@ -1906,7 +2386,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>103</v>
       </c>
@@ -1920,7 +2400,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>107</v>
       </c>
@@ -1934,7 +2414,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>111</v>
       </c>
@@ -1948,7 +2428,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>103</v>
       </c>
@@ -1962,7 +2442,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>107</v>
       </c>
@@ -1984,9 +2464,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D21"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2000,7 +2480,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -2014,7 +2494,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -2028,7 +2508,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -2042,7 +2522,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -2056,7 +2536,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>26</v>
       </c>
@@ -2070,7 +2550,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -2084,7 +2564,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>35</v>
       </c>
@@ -2098,7 +2578,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>39</v>
       </c>
@@ -2112,7 +2592,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>44</v>
       </c>
@@ -2126,7 +2606,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>48</v>
       </c>
@@ -2140,7 +2620,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>53</v>
       </c>
@@ -2154,7 +2634,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>57</v>
       </c>
@@ -2168,7 +2648,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>62</v>
       </c>
@@ -2182,7 +2662,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>66</v>
       </c>
@@ -2196,7 +2676,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>71</v>
       </c>
@@ -2210,7 +2690,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>75</v>
       </c>
@@ -2224,7 +2704,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>80</v>
       </c>
@@ -2238,7 +2718,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>84</v>
       </c>
@@ -2252,7 +2732,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>89</v>
       </c>
@@ -2266,7 +2746,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>94</v>
       </c>
@@ -2288,9 +2768,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G21"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2313,7 +2793,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -2336,7 +2816,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -2359,7 +2839,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -2382,7 +2862,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -2405,7 +2885,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>26</v>
       </c>
@@ -2428,7 +2908,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -2451,7 +2931,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>35</v>
       </c>
@@ -2474,7 +2954,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>39</v>
       </c>
@@ -2497,7 +2977,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>44</v>
       </c>
@@ -2520,7 +3000,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>48</v>
       </c>
@@ -2543,7 +3023,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>53</v>
       </c>
@@ -2566,7 +3046,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>57</v>
       </c>
@@ -2589,7 +3069,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>62</v>
       </c>
@@ -2612,7 +3092,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>66</v>
       </c>
@@ -2635,7 +3115,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>71</v>
       </c>
@@ -2658,7 +3138,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>75</v>
       </c>
@@ -2681,7 +3161,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>80</v>
       </c>
@@ -2704,7 +3184,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>84</v>
       </c>
@@ -2727,7 +3207,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>89</v>
       </c>
@@ -2750,7 +3230,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>94</v>
       </c>
@@ -2781,9 +3261,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:H21"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2809,7 +3289,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -2835,7 +3315,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -2861,7 +3341,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -2887,7 +3367,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -2913,7 +3393,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>26</v>
       </c>
@@ -2939,7 +3419,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -2965,7 +3445,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>35</v>
       </c>
@@ -2991,7 +3471,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>39</v>
       </c>
@@ -3017,7 +3497,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>44</v>
       </c>
@@ -3043,7 +3523,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>48</v>
       </c>
@@ -3069,7 +3549,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>53</v>
       </c>
@@ -3095,7 +3575,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>57</v>
       </c>
@@ -3121,7 +3601,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>62</v>
       </c>
@@ -3147,7 +3627,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>66</v>
       </c>
@@ -3173,7 +3653,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>71</v>
       </c>
@@ -3199,7 +3679,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>75</v>
       </c>
@@ -3225,7 +3705,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>80</v>
       </c>
@@ -3251,7 +3731,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>84</v>
       </c>
@@ -3277,7 +3757,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>89</v>
       </c>
@@ -3303,7 +3783,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>94</v>
       </c>
